--- a/docs/plantilla_carga_ordenes_servicio_2026.xlsx
+++ b/docs/plantilla_carga_ordenes_servicio_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\Xinergia\xinergiapro\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3575D4-E940-448C-84E0-53E4FBC8D38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E524586A-AD9D-46CA-8B96-30A0064BF221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6C8D27B-984A-4DC5-A1D1-BD94CC8774EE}"/>
   </bookViews>
@@ -537,12 +537,12 @@
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
